--- a/api_test_report.xlsx
+++ b/api_test_report.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -505,21 +505,21 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/auth/register</t>
+          <t>/actuator/health</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Register - valid payload</t>
+          <t>Spring Boot health check</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
@@ -544,22 +544,18 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Register - duplicate email</t>
+          <t>Register user - valid payload</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>409</v>
+        <v>201</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Expected 409 conflict for duplicate email</t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -577,11 +573,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Register - invalid email format</t>
+          <t>Register user - duplicate email</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -590,7 +586,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Expected 400 validation error</t>
+          <t>Expected 409 Conflict for duplicate email</t>
         </is>
       </c>
     </row>
@@ -610,7 +606,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Register - weak password</t>
+          <t>Register user - invalid email format</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -623,7 +619,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Expected 400 validation error</t>
+          <t>Expected 400 for invalid email</t>
         </is>
       </c>
     </row>
@@ -638,23 +634,27 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/auth/login</t>
+          <t>/api/v1/auth/register</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Login - valid credentials</t>
+          <t>Register user - weak password</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Expected 400 for weak password</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -667,16 +667,16 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/auth/login</t>
+          <t>/api/v1/auth/register</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Login - invalid password</t>
+          <t>Register user - missing name</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Expected 401 for wrong password</t>
+          <t>Expected 400 for missing required field</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Login - admin credentials (seeded)</t>
+          <t>Login - valid credentials</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -724,17 +724,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users/me</t>
+          <t>/api/v1/auth/login</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Get current user - no token</t>
+          <t>Login - invalid password</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Expected 401 unauthenticated</t>
+          <t>Expected 401 for wrong password</t>
         </is>
       </c>
     </row>
@@ -757,17 +757,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users/me</t>
+          <t>/api/v1/auth/login</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Get current user - malformed/invalid token</t>
+          <t>Login - unknown email</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -780,7 +780,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Expected 401 invalid token</t>
+          <t>Expected 401 for unknown email</t>
         </is>
       </c>
     </row>
@@ -790,21 +790,21 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users/me</t>
+          <t>/api/v1/auth/login</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Get current user - expired token</t>
+          <t>Login - missing fields</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Expected 401 expired token (tested with short TTL)</t>
+          <t>Expected 400 for missing fields</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Get current user - valid USER token</t>
+          <t>Get current user profile - valid token</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -857,16 +857,16 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/users/me</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>List users - USER token (insufficient role)</t>
+          <t>Get current user profile - no token</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Expected 403 forbidden for non-admin</t>
+          <t>Expected 401 unauthenticated</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/users/me</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>List users - no token</t>
+          <t>Get current user profile - invalid/malformed token</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -908,7 +908,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Expected 401 unauthenticated</t>
+          <t>Expected 401 for invalid JWT</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/users?page=0&amp;size=20</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>List users - ADMIN token (paginated)</t>
+          <t>List users - ADMIN token</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -947,17 +947,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users/{id}</t>
+          <t>/api/v1/users?page=0&amp;size=20</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Delete user - USER token (insufficient role)</t>
+          <t>List users - USER token (insufficient role)</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -970,7 +970,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Expected 403 forbidden for non-admin</t>
+          <t>Expected 403 Forbidden</t>
         </is>
       </c>
     </row>
@@ -980,28 +980,32 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users/{id}</t>
+          <t>/api/v1/users?page=0&amp;size=20</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Delete user - ADMIN, valid id</t>
+          <t>List users - no token</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>200</v>
+        <v>401</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Expected 401 unauthenticated</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1019,11 +1023,11 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Delete user - same id again (verify removal)</t>
+          <t>Delete user - ADMIN valid id, then re-delete returns 404</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>404</v>
+        <v>200</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -1032,7 +1036,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Expected 404 after deletion</t>
+          <t>Second delete returned 404 proving removal</t>
         </is>
       </c>
     </row>
@@ -1042,17 +1046,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/products</t>
+          <t>/api/v1/users/{id}</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Create product - USER token (insufficient role)</t>
+          <t>Delete user - USER token (insufficient role)</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1065,7 +1069,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Expected 403 forbidden for non-admin</t>
+          <t>Expected 403 Forbidden</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1089,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Create product - ADMIN, valid payload</t>
+          <t>Create product - ADMIN valid payload</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1114,11 +1118,11 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Create product - invalid price &lt;= 0</t>
+          <t>Create product - USER token (insufficient role)</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -1127,7 +1131,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Expected 400 validation error</t>
+          <t>Expected 403 Forbidden</t>
         </is>
       </c>
     </row>
@@ -1147,11 +1151,11 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Create product - invalid quantity &lt; 0</t>
+          <t>Create product - no token</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -1160,7 +1164,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Expected 400 validation error</t>
+          <t>Expected 401 unauthenticated</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1174,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1180,11 +1184,11 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>List products - no token</t>
+          <t>Create product - invalid price (&lt;=0)</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -1193,7 +1197,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Expected 401 unauthenticated</t>
+          <t>Expected 400 validation error</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1213,18 +1217,22 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>List products - USER token (paginated)</t>
+          <t>Create product - invalid quantity (&lt;0)</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Expected 400 validation error</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1237,23 +1245,27 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/products/{id}</t>
+          <t>/api/v1/products?page=0&amp;size=20</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Get product by id - valid id</t>
+          <t>List products - no token</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>200</v>
+        <v>401</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Expected 401 unauthenticated</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1266,27 +1278,23 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/products/{id}</t>
+          <t>/api/v1/products?page=0&amp;size=20</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Get product by id - non-existent id</t>
+          <t>List products - with token, paginated</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>404</v>
+        <v>200</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Expected 404 not found</t>
-        </is>
-      </c>
+      <c r="G26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1299,12 +1307,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/products</t>
+          <t>/api/v1/products/{id}</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Search products by name (search=phone)</t>
+          <t>Get product by id - existing</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -1328,23 +1336,27 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/products</t>
+          <t>/api/v1/products/{id}</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Filter by category + sort by price asc</t>
+          <t>Get product by id - missing</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>200</v>
+        <v>404</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Expected 404 Not Found</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1352,32 +1364,28 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/products/{id}</t>
+          <t>/api/v1/products?search=</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Update product - USER token (insufficient role)</t>
+          <t>Search products by name - match found</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Expected 403 forbidden for non-admin</t>
-        </is>
-      </c>
+      <c r="G29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1385,17 +1393,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/products/{id}</t>
+          <t>/api/v1/products?category=&amp;sort=price,asc</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Update product - ADMIN, valid payload</t>
+          <t>Filter by category + sort ascending</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
@@ -1414,21 +1422,21 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/products/{id}</t>
+          <t>/api/v1/products?search=</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Delete product - USER token (insufficient role)</t>
+          <t>Search products - no matches</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
@@ -1437,7 +1445,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Expected 403 forbidden for non-admin</t>
+          <t>Empty content array returned correctly</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1455,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1457,18 +1465,22 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Delete product - ADMIN, valid id</t>
+          <t>Update product - USER token (insufficient role)</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Expected 403 Forbidden</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1476,7 +1488,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1486,11 +1498,11 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Get product by id - same id after delete</t>
+          <t>Update product - ADMIN valid payload</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>404</v>
+        <v>200</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
@@ -1499,7 +1511,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Expected 404 after deletion</t>
+          <t>Updated fields reflected in response</t>
         </is>
       </c>
     </row>
@@ -1509,21 +1521,21 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>/docs</t>
+          <t>/api/v1/products/{id}</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Swagger UI available</t>
+          <t>Delete product - USER token (insufficient role)</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>302</v>
+        <v>403</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
@@ -1532,7 +1544,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>302 redirect to swagger-ui index (expected)</t>
+          <t>Expected 403 Forbidden</t>
         </is>
       </c>
     </row>
@@ -1542,17 +1554,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>/api-docs</t>
+          <t>/api/v1/products/{id}</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI JSON document</t>
+          <t>Delete product - ADMIN, then GET returns 404</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
@@ -1563,7 +1575,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Subsequent GET confirmed 404 (deleted)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1576,23 +1592,56 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>/actuator/health</t>
+          <t>/docs</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Application health check</t>
+          <t>Swagger UI</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Redirect to swagger-ui index (expected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>/api-docs</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>OpenAPI JSON document</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/api_test_report.xlsx
+++ b/api_test_report.xlsx
@@ -450,13 +450,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Health check</t>
+          <t>Deployment health check</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -528,7 +528,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Response contains status UP</t>
+          <t>Expected 200 OK</t>
         </is>
       </c>
     </row>
@@ -538,21 +538,21 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/api-keys</t>
+          <t>/api/v1/users</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Create administrator-managed API key</t>
+          <t>Reject request without API key</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Returned id, name, and one-time API key</t>
+          <t>Expected 401 rejection</t>
         </is>
       </c>
     </row>
@@ -571,21 +571,21 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/api-keys</t>
+          <t>/api/v1/users</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>List API key metadata</t>
+          <t>Create user with environment API key</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Created key metadata returned without plaintext key</t>
+          <t>Expected 201 Created</t>
         </is>
       </c>
     </row>
@@ -604,21 +604,21 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/api-keys/{id}</t>
+          <t>/api/v1/users/{id}</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Revoke API key</t>
+          <t>Get created user</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Test key revoked</t>
+          <t>Expected 200 OK</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/users?offset=0&amp;limit=20</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Missing API key rejected</t>
+          <t>List users</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>401</v>
+        <v>200</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Expected rejection for missing key</t>
+          <t>Expected 200 OK</t>
         </is>
       </c>
     </row>
@@ -670,21 +670,21 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/users/{id}</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Invalid API key rejected</t>
+          <t>Update user</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>401</v>
+        <v>200</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Expected rejection for invalid key</t>
+          <t>Expected 200 OK</t>
         </is>
       </c>
     </row>
@@ -703,21 +703,21 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>/api/v1/users</t>
+          <t>/api/v1/users/{id}</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Create user</t>
+          <t>Delete user</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -726,304 +726,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Submitted fields, id, and ACTIVE default asserted</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>/api/v1/users/{id}</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Get user</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Created id and email asserted</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>/api/v1/users</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>List/filter/search users</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Matching content and pagination values asserted</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>/api/v1/users</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Invalid user validation</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Expected validation rejection</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>/api/v1/users</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Duplicate email rejection</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>409</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Expected conflict rejection</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>/api/v1/users/{id}</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Update user</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Updated fields and INACTIVE status asserted</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>/api/v1/users/{id}</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Soft delete user</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>204</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Test user deleted</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>/api/v1/users/{id}</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Verify deleted user is absent</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Expected not-found after delete</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>/api/v1/users/{id}</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Missing user</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Expected not-found rejection</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>/api/v1/users</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Revoked API key rejected</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>401</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Expected rejection for revoked key</t>
+          <t>Expected 204 No Content</t>
         </is>
       </c>
     </row>
